--- a/data/trans_dic/P2A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,48; 49,68</t>
+          <t>40,59; 50,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,48; 56,5</t>
+          <t>46,15; 56,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,38; 51,15</t>
+          <t>40,51; 50,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,65; 42,57</t>
+          <t>33,76; 42,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,99; 57,56</t>
+          <t>45,42; 56,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,46; 59,12</t>
+          <t>47,39; 59,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,2; 58,1</t>
+          <t>47,12; 57,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,07; 43,11</t>
+          <t>35,21; 43,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,9; 51,27</t>
+          <t>44,07; 51,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47,64; 55,75</t>
+          <t>48,29; 55,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,16; 52,76</t>
+          <t>45,38; 52,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,66; 41,43</t>
+          <t>35,2; 41,46</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,97; 52,32</t>
+          <t>42,37; 53,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,61; 58,6</t>
+          <t>48,51; 59,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,41; 54,55</t>
+          <t>43,68; 54,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,25; 39,64</t>
+          <t>30,31; 39,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,13; 60,43</t>
+          <t>49,4; 60,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,95; 68,37</t>
+          <t>56,84; 67,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,86; 56,24</t>
+          <t>46,24; 56,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,4; 40,49</t>
+          <t>32,37; 40,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,82; 55,27</t>
+          <t>47,57; 55,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,49; 61,6</t>
+          <t>54,2; 61,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,57; 53,8</t>
+          <t>46,65; 53,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,78; 38,78</t>
+          <t>32,89; 38,85</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,36; 52,8</t>
+          <t>44,41; 52,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54,61; 62,77</t>
+          <t>55,12; 62,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,23; 63,07</t>
+          <t>54,39; 62,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,22; 41,88</t>
+          <t>10,73; 42,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,39; 68,81</t>
+          <t>54,6; 69,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,05; 76,37</t>
+          <t>64,42; 76,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,65; 73,03</t>
+          <t>59,03; 73,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,51; 57,18</t>
+          <t>44,97; 57,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47,91; 55,6</t>
+          <t>47,74; 55,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,1; 65,84</t>
+          <t>59,15; 65,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56,69; 64,31</t>
+          <t>56,54; 64,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,77; 44,57</t>
+          <t>14,67; 44,39</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,18; 55,8</t>
+          <t>50,17; 55,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,7; 61,51</t>
+          <t>55,65; 61,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,87; 57,96</t>
+          <t>51,92; 58,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40,64; 47,46</t>
+          <t>40,37; 47,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,34; 65,6</t>
+          <t>58,47; 66,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,71; 68,52</t>
+          <t>61,51; 68,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,12; 59,88</t>
+          <t>53,06; 60,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,84; 76,42</t>
+          <t>41,97; 73,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,35; 58,65</t>
+          <t>54,16; 58,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,84; 63,57</t>
+          <t>59,04; 63,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53,12; 57,65</t>
+          <t>53,23; 57,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,8; 63,16</t>
+          <t>42,87; 65,62</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,64; 58,32</t>
+          <t>47,44; 58,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,4; 63,04</t>
+          <t>54,79; 63,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,76; 60,77</t>
+          <t>52,05; 60,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,49; 54,13</t>
+          <t>44,11; 53,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,28; 69,52</t>
+          <t>60,27; 69,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,73; 78,18</t>
+          <t>71,55; 78,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,28; 76,52</t>
+          <t>70,13; 76,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,52; 54,53</t>
+          <t>36,5; 55,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,1; 63,78</t>
+          <t>57,14; 63,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65,63; 71,29</t>
+          <t>65,85; 71,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62,95; 68,17</t>
+          <t>63,11; 68,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,14; 52,66</t>
+          <t>40,06; 52,65</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,34; 32,26</t>
+          <t>22,47; 32,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,65; 44,18</t>
+          <t>32,84; 45,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,97; 40,72</t>
+          <t>29,31; 40,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,92; 37,66</t>
+          <t>18,89; 39,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67,41; 72,48</t>
+          <t>67,3; 72,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,81; 76,31</t>
+          <t>71,48; 76,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,89; 72,49</t>
+          <t>66,97; 72,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49,01; 55,72</t>
+          <t>48,75; 55,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,42; 64,2</t>
+          <t>59,35; 64,35</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64,43; 69,87</t>
+          <t>64,34; 69,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59,98; 65,33</t>
+          <t>59,98; 65,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42,73; 49,94</t>
+          <t>42,57; 49,9</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,43; 50,06</t>
+          <t>46,49; 49,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>53,86; 57,28</t>
+          <t>53,91; 57,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50,62; 54,16</t>
+          <t>50,7; 54,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,46; 41,31</t>
+          <t>30,32; 41,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>62,21; 65,52</t>
+          <t>62,33; 65,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,73; 70,66</t>
+          <t>67,57; 70,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,91; 65,3</t>
+          <t>61,94; 65,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,35; 58,72</t>
+          <t>44,75; 58,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>54,88; 57,32</t>
+          <t>54,74; 57,19</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61,32; 63,64</t>
+          <t>61,34; 63,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56,91; 59,32</t>
+          <t>56,9; 59,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,76; 48,0</t>
+          <t>38,9; 47,91</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>191802; 235359</t>
+          <t>192286; 237502</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>203237; 247046</t>
+          <t>201787; 245575</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>177541; 219488</t>
+          <t>173838; 218487</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>170001; 215048</t>
+          <t>170572; 214362</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>141029; 176513</t>
+          <t>139284; 174450</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>149241; 185908</t>
+          <t>149005; 187352</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>163827; 201646</t>
+          <t>163530; 200790</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>156945; 192883</t>
+          <t>157562; 193581</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>342615; 400174</t>
+          <t>343978; 400656</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>358096; 419060</t>
+          <t>362957; 418163</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>350513; 409503</t>
+          <t>352197; 409242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>339687; 394739</t>
+          <t>335320; 394963</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>154016; 191990</t>
+          <t>155476; 196732</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>199372; 245396</t>
+          <t>203156; 247500</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>167513; 205787</t>
+          <t>164790; 205027</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>136801; 179251</t>
+          <t>137056; 180291</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>186404; 224728</t>
+          <t>183715; 224588</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>192503; 231109</t>
+          <t>192141; 229626</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>170736; 209356</t>
+          <t>172152; 210874</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>123958; 154911</t>
+          <t>123857; 156571</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>353290; 408363</t>
+          <t>351475; 406946</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>404832; 466164</t>
+          <t>410190; 466156</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>349031; 403236</t>
+          <t>349641; 402772</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>273675; 323773</t>
+          <t>274535; 324329</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>240613; 286402</t>
+          <t>240876; 286019</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>343711; 395104</t>
+          <t>346914; 395833</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>283037; 329155</t>
+          <t>283873; 327344</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61613; 279876</t>
+          <t>71716; 281349</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>91260; 115443</t>
+          <t>91602; 116031</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>169207; 198649</t>
+          <t>167569; 198250</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97436; 121321</t>
+          <t>98064; 122223</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>74293; 95440</t>
+          <t>75065; 96150</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>340254; 394837</t>
+          <t>339052; 394902</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>525739; 585711</t>
+          <t>526135; 585905</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>390029; 442497</t>
+          <t>389021; 442870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>106677; 372205</t>
+          <t>122511; 370713</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>621357; 690996</t>
+          <t>621270; 691109</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>645561; 712902</t>
+          <t>644991; 714982</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>596325; 666369</t>
+          <t>596866; 667128</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>420541; 491085</t>
+          <t>417797; 488162</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>416748; 468604</t>
+          <t>417621; 472871</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>473131; 525345</t>
+          <t>471541; 526086</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>438713; 494556</t>
+          <t>438178; 496588</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>409252; 747461</t>
+          <t>410481; 722863</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1061191; 1145218</t>
+          <t>1057520; 1144258</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1133020; 1224203</t>
+          <t>1136997; 1227122</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1049466; 1138850</t>
+          <t>1051499; 1142222</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>861433; 1271343</t>
+          <t>862901; 1320838</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>167009; 204436</t>
+          <t>166302; 205116</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>277750; 321897</t>
+          <t>279756; 324649</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>327506; 377192</t>
+          <t>323100; 374586</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211359; 257141</t>
+          <t>209552; 255959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>348514; 395389</t>
+          <t>342814; 393116</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>546242; 595330</t>
+          <t>544832; 596059</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>518830; 564926</t>
+          <t>517737; 565542</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>290456; 458798</t>
+          <t>307054; 464493</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>524890; 586371</t>
+          <t>525283; 582944</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>834944; 906852</t>
+          <t>837628; 905339</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>855515; 926422</t>
+          <t>857658; 928382</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>528375; 693161</t>
+          <t>527387; 693123</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66609; 96195</t>
+          <t>66992; 97671</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87125; 117901</t>
+          <t>87631; 120710</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86071; 116931</t>
+          <t>84162; 115095</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43087; 90578</t>
+          <t>45426; 94059</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>841811; 905163</t>
+          <t>840460; 903894</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>785501; 846563</t>
+          <t>793011; 848115</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>723755; 784376</t>
+          <t>724648; 785705</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>373170; 424200</t>
+          <t>371159; 423221</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>919220; 993202</t>
+          <t>918133; 995449</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>886750; 961567</t>
+          <t>885439; 957364</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>821220; 894521</t>
+          <t>821166; 893120</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>428121; 500340</t>
+          <t>426493; 499917</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1518293; 1637052</t>
+          <t>1520192; 1630168</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1842873; 1959961</t>
+          <t>1844622; 1964732</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1713854; 1833621</t>
+          <t>1716627; 1831175</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>994699; 1394556</t>
+          <t>1023600; 1393530</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2101418; 2213359</t>
+          <t>2105467; 2214502</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2404377; 2508480</t>
+          <t>2398654; 2511239</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2186543; 2306008</t>
+          <t>2187468; 2303831</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1586693; 2101036</t>
+          <t>1600943; 2078292</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3648345; 3810487</t>
+          <t>3639230; 3802255</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4275508; 4437010</t>
+          <t>4276637; 4435777</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3936666; 4103094</t>
+          <t>3935775; 4101340</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2695422; 3337636</t>
+          <t>2705141; 3331369</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,41%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,59; 50,13</t>
+          <t>40,22; 49,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,15; 56,17</t>
+          <t>46,28; 56,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,51; 50,92</t>
+          <t>40,86; 50,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,76; 42,43</t>
+          <t>33,29; 41,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,42; 56,88</t>
+          <t>45,04; 57,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,39; 59,58</t>
+          <t>47,0; 59,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,12; 57,86</t>
+          <t>47,09; 57,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,21; 43,26</t>
+          <t>35,82; 43,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,07; 51,34</t>
+          <t>43,45; 51,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,29; 55,63</t>
+          <t>48,15; 55,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,38; 52,73</t>
+          <t>44,91; 52,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,2; 41,46</t>
+          <t>35,71; 41,41</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,37; 53,62</t>
+          <t>42,15; 52,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,51; 59,1</t>
+          <t>48,31; 58,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,68; 54,35</t>
+          <t>44,56; 55,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,31; 39,87</t>
+          <t>29,98; 38,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,4; 60,39</t>
+          <t>49,66; 60,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,84; 67,93</t>
+          <t>57,04; 67,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,24; 56,64</t>
+          <t>46,19; 56,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,37; 40,93</t>
+          <t>31,94; 39,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,57; 55,08</t>
+          <t>47,77; 55,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54,2; 61,59</t>
+          <t>53,89; 61,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,65; 53,74</t>
+          <t>46,44; 54,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,89; 38,85</t>
+          <t>32,28; 38,09</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,41; 52,73</t>
+          <t>44,23; 53,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,12; 62,89</t>
+          <t>54,57; 62,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,39; 62,72</t>
+          <t>54,19; 62,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,73; 42,1</t>
+          <t>34,89; 43,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,6; 69,16</t>
+          <t>54,68; 69,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,42; 76,21</t>
+          <t>64,81; 76,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,03; 73,57</t>
+          <t>58,69; 73,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,97; 57,61</t>
+          <t>44,34; 56,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47,74; 55,61</t>
+          <t>48,06; 55,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,15; 65,87</t>
+          <t>59,0; 65,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56,54; 64,37</t>
+          <t>56,93; 64,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,67; 44,39</t>
+          <t>39,3; 46,55</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,17; 55,81</t>
+          <t>50,23; 55,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,65; 61,69</t>
+          <t>55,76; 61,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,92; 58,03</t>
+          <t>52,21; 57,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40,37; 47,17</t>
+          <t>39,92; 46,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,47; 66,2</t>
+          <t>58,91; 65,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,51; 68,62</t>
+          <t>61,55; 68,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,06; 60,13</t>
+          <t>53,1; 59,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,97; 73,91</t>
+          <t>39,62; 45,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54,16; 58,6</t>
+          <t>53,96; 58,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,04; 63,72</t>
+          <t>59,06; 63,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53,23; 57,82</t>
+          <t>53,34; 57,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,87; 65,62</t>
+          <t>40,65; 44,92</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,44; 58,51</t>
+          <t>47,69; 58,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,79; 63,58</t>
+          <t>54,67; 63,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,05; 60,35</t>
+          <t>52,69; 60,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,11; 53,88</t>
+          <t>39,22; 48,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>60,27; 69,12</t>
+          <t>61,55; 69,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,55; 78,27</t>
+          <t>71,45; 77,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,13; 76,61</t>
+          <t>70,32; 76,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,5; 55,21</t>
+          <t>50,11; 55,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,14; 63,41</t>
+          <t>57,36; 63,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65,85; 71,17</t>
+          <t>65,81; 71,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63,11; 68,32</t>
+          <t>62,93; 68,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,06; 52,65</t>
+          <t>46,87; 51,74</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,47; 32,75</t>
+          <t>22,37; 32,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,84; 45,23</t>
+          <t>31,99; 44,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,31; 40,08</t>
+          <t>29,22; 40,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,89; 39,11</t>
+          <t>18,04; 34,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67,3; 72,38</t>
+          <t>67,24; 72,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,48; 76,45</t>
+          <t>71,08; 76,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,97; 72,61</t>
+          <t>67,08; 72,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>48,75; 55,59</t>
+          <t>48,25; 54,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,35; 64,35</t>
+          <t>59,09; 64,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64,34; 69,56</t>
+          <t>64,27; 69,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59,98; 65,23</t>
+          <t>59,8; 65,31</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42,57; 49,9</t>
+          <t>42,57; 49,37</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,49; 49,85</t>
+          <t>46,4; 49,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>53,91; 57,42</t>
+          <t>53,92; 57,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50,7; 54,09</t>
+          <t>50,65; 54,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,32; 41,28</t>
+          <t>37,38; 41,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>62,33; 65,55</t>
+          <t>61,91; 65,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,57; 70,74</t>
+          <t>67,55; 70,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,94; 65,23</t>
+          <t>61,98; 65,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,75; 58,09</t>
+          <t>44,87; 47,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>54,74; 57,19</t>
+          <t>54,91; 57,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61,34; 63,62</t>
+          <t>61,28; 63,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56,9; 59,29</t>
+          <t>56,91; 59,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,9; 47,91</t>
+          <t>41,76; 44,06</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191435</t>
+          <t>207276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>175364</t>
+          <t>191858</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>366799</t>
+          <t>399134</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>192286; 237502</t>
+          <t>190534; 236262</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>201787; 245575</t>
+          <t>202354; 245415</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173838; 218487</t>
+          <t>175348; 218297</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>170572; 214362</t>
+          <t>183306; 229439</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>139284; 174450</t>
+          <t>138134; 174960</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>149005; 187352</t>
+          <t>147778; 186100</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>163530; 200790</t>
+          <t>163414; 200511</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>157562; 193581</t>
+          <t>174971; 212158</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>343978; 400656</t>
+          <t>339089; 399707</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>362957; 418163</t>
+          <t>361912; 420084</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>352197; 409242</t>
+          <t>348601; 405633</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>335320; 394963</t>
+          <t>371026; 430300</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>159072</t>
+          <t>165889</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>139461</t>
+          <t>152168</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>298533</t>
+          <t>318058</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>155476; 196732</t>
+          <t>154671; 193353</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>203156; 247500</t>
+          <t>202333; 246816</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>164790; 205027</t>
+          <t>168083; 208188</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>137056; 180291</t>
+          <t>144852; 186745</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>183715; 224588</t>
+          <t>184657; 223901</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>192141; 229626</t>
+          <t>192813; 229448</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>172152; 210874</t>
+          <t>171966; 209394</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>123857; 156571</t>
+          <t>135165; 168913</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>351475; 406946</t>
+          <t>352908; 408506</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>410190; 466156</t>
+          <t>407832; 466832</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>349641; 402772</t>
+          <t>348104; 404844</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>274535; 324329</t>
+          <t>292580; 345191</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172241</t>
+          <t>186247</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84850</t>
+          <t>94440</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>257092</t>
+          <t>280687</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>240876; 286019</t>
+          <t>239911; 288471</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>346914; 395833</t>
+          <t>343465; 395495</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>283873; 327344</t>
+          <t>282800; 328212</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71716; 281349</t>
+          <t>164559; 207282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>91602; 116031</t>
+          <t>91744; 116767</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>167569; 198250</t>
+          <t>168584; 199359</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98064; 122223</t>
+          <t>97502; 121840</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75065; 96150</t>
+          <t>83145; 105943</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>339052; 394902</t>
+          <t>341326; 393436</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>526135; 585905</t>
+          <t>524861; 583345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>389021; 442870</t>
+          <t>391716; 443236</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>122511; 370713</t>
+          <t>259004; 306811</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>455146</t>
+          <t>485299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>537496</t>
+          <t>365991</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>992642</t>
+          <t>851289</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>621270; 691109</t>
+          <t>622050; 689868</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>644991; 714982</t>
+          <t>646305; 717409</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>596866; 667128</t>
+          <t>600234; 665943</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>417797; 488162</t>
+          <t>451842; 521739</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>417621; 472871</t>
+          <t>420780; 471240</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>471541; 526086</t>
+          <t>471909; 527772</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>438178; 496588</t>
+          <t>438547; 494852</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>410481; 722863</t>
+          <t>341186; 392478</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1057520; 1144258</t>
+          <t>1053709; 1143685</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1136997; 1227122</t>
+          <t>1137231; 1223385</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1051499; 1142222</t>
+          <t>1053801; 1141810</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>862901; 1320838</t>
+          <t>810241; 895226</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>232177</t>
+          <t>249539</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>405600</t>
+          <t>441450</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>637777</t>
+          <t>690989</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>166302; 205116</t>
+          <t>167185; 204220</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>279756; 324649</t>
+          <t>279151; 322193</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>323100; 374586</t>
+          <t>327048; 374945</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>209552; 255959</t>
+          <t>222774; 273929</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>342814; 393116</t>
+          <t>350061; 396199</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>544832; 596059</t>
+          <t>544120; 593920</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>517737; 565542</t>
+          <t>519143; 565599</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>307054; 464493</t>
+          <t>416351; 464140</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>525283; 582944</t>
+          <t>527323; 587119</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837628; 905339</t>
+          <t>837216; 906927</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>857658; 928382</t>
+          <t>855131; 928339</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>527387; 693123</t>
+          <t>655589; 723703</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65180</t>
+          <t>59841</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>398207</t>
+          <t>437357</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>463386</t>
+          <t>497199</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66992; 97671</t>
+          <t>66693; 97030</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87631; 120710</t>
+          <t>85371; 119380</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84162; 115095</t>
+          <t>83899; 115858</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45426; 94059</t>
+          <t>42796; 81619</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>840460; 903894</t>
+          <t>839657; 903109</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>793011; 848115</t>
+          <t>788529; 847837</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>724648; 785705</t>
+          <t>725855; 784248</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>371159; 423221</t>
+          <t>407342; 464035</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>918133; 995449</t>
+          <t>914031; 990390</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>885439; 957364</t>
+          <t>884491; 956616</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>821166; 893120</t>
+          <t>818813; 894184</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>426493; 499917</t>
+          <t>460351; 533897</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1275250</t>
+          <t>1354092</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1740979</t>
+          <t>1683263</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3016229</t>
+          <t>3037355</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1520192; 1630168</t>
+          <t>1517361; 1633135</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1844622; 1964732</t>
+          <t>1845051; 1960755</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1716627; 1831175</t>
+          <t>1714948; 1832045</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1023600; 1393530</t>
+          <t>1286935; 1412183</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2105467; 2214502</t>
+          <t>2091553; 2211876</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2398654; 2511239</t>
+          <t>2398225; 2513983</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2187468; 2303831</t>
+          <t>2188861; 2305965</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1600943; 2078292</t>
+          <t>1631368; 1737254</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3639230; 3802255</t>
+          <t>3650657; 3812577</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4276637; 4435777</t>
+          <t>4272334; 4436189</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3935775; 4101340</t>
+          <t>3936735; 4112446</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2705141; 3331369</t>
+          <t>2955531; 3118718</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
